--- a/data/trans_orig/IQ2606_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ2606_R-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean crema solar con factor de protección de 50 o más en 2012 (tasa de respuesta: 99,85%)</t>
+          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más en 2012 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75241</t>
+          <t>75139</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92651</t>
+          <t>92061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62416</t>
+          <t>63158</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81115</t>
+          <t>79731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>142654</t>
+          <t>143257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>167696</t>
+          <t>167840</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,71%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24146</t>
+          <t>24270</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15067</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29372</t>
+          <t>29219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32168</t>
+          <t>30750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49838</t>
+          <t>49963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>17761</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>15351</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15013</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30143</t>
+          <t>30358</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17181</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19716</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32933</t>
+          <t>32728</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99144</t>
+          <t>99933</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124521</t>
+          <t>124762</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109776</t>
+          <t>109575</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136643</t>
+          <t>137412</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>217756</t>
+          <t>217385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>254203</t>
+          <t>255892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48805</t>
+          <t>48796</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70805</t>
+          <t>71414</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52270</t>
+          <t>51454</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74145</t>
+          <t>74771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107600</t>
+          <t>106909</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137230</t>
+          <t>137888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27234</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44675</t>
+          <t>45616</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30293</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49667</t>
+          <t>50391</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>61364</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>89507</t>
+          <t>88552</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20978</t>
+          <t>19732</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14915</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30962</t>
+          <t>31556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13430</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27428</t>
+          <t>27959</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>23537</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42724</t>
+          <t>41490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40864</t>
+          <t>40271</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63263</t>
+          <t>63864</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43926</t>
+          <t>43372</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63498</t>
+          <t>63371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44189</t>
+          <t>44192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63099</t>
+          <t>63085</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92824</t>
+          <t>93344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121311</t>
+          <t>121122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27697</t>
+          <t>28632</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45961</t>
+          <t>44940</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22804</t>
+          <t>22715</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39597</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55525</t>
+          <t>54212</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79429</t>
+          <t>79496</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22222</t>
+          <t>21216</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37580</t>
+          <t>38582</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>19581</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35935</t>
+          <t>35032</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>45674</t>
+          <t>45110</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>67273</t>
+          <t>68200</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7015</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>18278</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11172</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24549</t>
+          <t>24115</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20922</t>
+          <t>20753</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38570</t>
+          <t>37588</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18724</t>
+          <t>18943</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34981</t>
+          <t>34781</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24286</t>
+          <t>22962</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40334</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46799</t>
+          <t>46881</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>70325</t>
+          <t>69969</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25174</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42918</t>
+          <t>41785</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23267</t>
+          <t>23165</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39579</t>
+          <t>39684</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50920</t>
+          <t>52605</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75177</t>
+          <t>76146</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24417</t>
+          <t>23913</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41919</t>
+          <t>40787</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18346</t>
+          <t>18486</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33842</t>
+          <t>33289</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47012</t>
+          <t>46681</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>69573</t>
+          <t>68988</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>52213</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>33574</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>51355</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>72772</t>
+          <t>72442</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>98197</t>
+          <t>97717</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26902</t>
+          <t>25679</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24127</t>
+          <t>23172</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41148</t>
+          <t>39312</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39424</t>
+          <t>39645</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59849</t>
+          <t>60349</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35746</t>
+          <t>35222</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54255</t>
+          <t>54138</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>41956</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61601</t>
+          <t>61003</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>80989</t>
+          <t>81339</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>107838</t>
+          <t>107233</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>262610</t>
+          <t>263257</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>303782</t>
+          <t>302972</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>255898</t>
+          <t>257422</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>300149</t>
+          <t>298582</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>530073</t>
+          <t>531491</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>589514</t>
+          <t>592603</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>131336</t>
+          <t>127320</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>168168</t>
+          <t>163788</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>122202</t>
+          <t>122620</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>157814</t>
+          <t>157571</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>262721</t>
+          <t>262000</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>310707</t>
+          <t>311277</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>102509</t>
+          <t>103738</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>135199</t>
+          <t>135123</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>103871</t>
+          <t>102987</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>136504</t>
+          <t>137286</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>215554</t>
+          <t>215037</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>261279</t>
+          <t>263465</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31645</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>51483</t>
+          <t>52114</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>51185</t>
+          <t>50427</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>75860</t>
+          <t>75573</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>87039</t>
+          <t>87210</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>120807</t>
+          <t>121655</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>87349</t>
+          <t>86629</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>117310</t>
+          <t>119654</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>110408</t>
+          <t>109838</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>144943</t>
+          <t>144588</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>206712</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>252557</t>
+          <t>250885</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean crema solar con factor de protección de 50 o más en 2016 (tasa de respuesta: 99,71%)</t>
+          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más en 2016 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49680</t>
+          <t>50244</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67550</t>
+          <t>67994</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54022</t>
+          <t>54767</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70897</t>
+          <t>72045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110509</t>
+          <t>110379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134236</t>
+          <t>135091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,89%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19494</t>
+          <t>18776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>33204</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19390</t>
+          <t>19540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34099</t>
+          <t>33319</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42328</t>
+          <t>42938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62984</t>
+          <t>62235</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>11014</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15931</t>
+          <t>16339</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22678</t>
+          <t>22669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37494</t>
+          <t>37877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26421</t>
+          <t>26283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39717</t>
+          <t>38890</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58889</t>
+          <t>58924</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99151</t>
+          <t>99868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121594</t>
+          <t>122123</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>121130</t>
+          <t>121189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147685</t>
+          <t>147398</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>226122</t>
+          <t>225958</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>261826</t>
+          <t>261504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45388</t>
+          <t>46390</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65274</t>
+          <t>66242</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67154</t>
+          <t>66835</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91046</t>
+          <t>90242</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>118813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>150108</t>
+          <t>150956</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19969</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36158</t>
+          <t>36333</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44297</t>
+          <t>44793</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>67378</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10252</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14402</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20656</t>
+          <t>20879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16258</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29400</t>
+          <t>29185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75484</t>
+          <t>74227</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97152</t>
+          <t>96917</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69400</t>
+          <t>70109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92456</t>
+          <t>91861</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149871</t>
+          <t>150955</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>181986</t>
+          <t>183206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48290</t>
+          <t>48028</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68774</t>
+          <t>68757</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45614</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66509</t>
+          <t>65579</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>98511</t>
+          <t>99230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>129804</t>
+          <t>128086</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21352</t>
+          <t>20799</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37760</t>
+          <t>37373</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25147</t>
+          <t>25136</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41969</t>
+          <t>43080</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50361</t>
+          <t>49937</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74654</t>
+          <t>74466</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14486</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24370</t>
+          <t>24041</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16364</t>
+          <t>15863</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27277</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45101</t>
+          <t>44610</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65318</t>
+          <t>65162</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37215</t>
+          <t>37272</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57246</t>
+          <t>55892</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87881</t>
+          <t>87681</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114993</t>
+          <t>115542</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>47669</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>66521</t>
+          <t>67705</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>46577</t>
+          <t>47803</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>67619</t>
+          <t>68506</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>99675</t>
+          <t>98890</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>127530</t>
+          <t>129691</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19782</t>
+          <t>20270</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35779</t>
+          <t>36504</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>15660</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30718</t>
+          <t>29744</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39056</t>
+          <t>39463</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>60910</t>
+          <t>61159</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>11818</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22191</t>
+          <t>23175</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29359</t>
+          <t>29313</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21440</t>
+          <t>21522</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>38240</t>
+          <t>37331</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25537</t>
+          <t>24934</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42637</t>
+          <t>42692</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>51939</t>
+          <t>51217</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>74811</t>
+          <t>75244</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>289621</t>
+          <t>289816</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>333482</t>
+          <t>332066</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>302122</t>
+          <t>303266</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>347948</t>
+          <t>344895</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>602629</t>
+          <t>601467</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>665812</t>
+          <t>660577</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>176306</t>
+          <t>177377</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>215474</t>
+          <t>215385</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>195438</t>
+          <t>194821</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>237246</t>
+          <t>236489</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>386831</t>
+          <t>383209</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>441894</t>
+          <t>442247</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>73816</t>
+          <t>73072</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>102415</t>
+          <t>103446</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>76382</t>
+          <t>75582</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>104913</t>
+          <t>105181</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>157603</t>
+          <t>157755</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>197712</t>
+          <t>197887</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30111</t>
+          <t>30560</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45743</t>
+          <t>45178</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>45057</t>
+          <t>44658</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>70024</t>
+          <t>69743</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>64533</t>
+          <t>63485</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>91578</t>
+          <t>91152</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>58996</t>
+          <t>59772</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>86002</t>
+          <t>86006</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>132218</t>
+          <t>132328</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>170907</t>
+          <t>172607</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean crema solar con factor de protección de 50 o más en 2023 (tasa de respuesta: 99,38%)</t>
+          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11429</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>13727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>20831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>74,23%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13379</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20199</t>
+          <t>20425</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25843</t>
+          <t>25687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>28381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43743</t>
+          <t>42170</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>53,31%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22549</t>
+          <t>22820</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24256</t>
+          <t>24310</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>29709</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43912</t>
+          <t>43471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>843</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>769</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16907</t>
+          <t>16448</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17127</t>
+          <t>17061</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32537</t>
+          <t>31957</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27278</t>
+          <t>26231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45504</t>
+          <t>44365</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>46,25%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13661</t>
+          <t>13934</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25867</t>
+          <t>26567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33191</t>
+          <t>32951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36587</t>
+          <t>35333</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55302</t>
+          <t>55144</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,49%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11572</t>
+          <t>11743</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>384</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>957</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>16325</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28530</t>
+          <t>28939</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27054</t>
+          <t>26532</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32315</t>
+          <t>32121</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51815</t>
+          <t>51022</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25583</t>
+          <t>26273</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33466</t>
+          <t>34227</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51738</t>
+          <t>51743</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51277</t>
+          <t>52486</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>73690</t>
+          <t>73764</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15701</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15612</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13945</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27492</t>
+          <t>27878</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>854</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>880</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>9975</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48520</t>
+          <t>48120</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>67838</t>
+          <t>68931</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59502</t>
+          <t>59679</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>84193</t>
+          <t>86420</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>112921</t>
+          <t>115004</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>145770</t>
+          <t>145954</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50927</t>
+          <t>51277</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>71403</t>
+          <t>71439</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>79353</t>
+          <t>79137</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>107507</t>
+          <t>105985</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>138056</t>
+          <t>136862</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>173302</t>
+          <t>171846</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25390</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13091</t>
+          <t>13480</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27917</t>
+          <t>27379</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>47392</t>
+          <t>48106</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,44 +11098,44 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>2425</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>6535</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>2425</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>6541</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
           <t>3,41%</t>
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
